--- a/AggregatedResults.xlsx
+++ b/AggregatedResults.xlsx
@@ -13251,7 +13251,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ony</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -13266,7 +13266,7 @@
         <v>14</v>
       </c>
       <c r="F218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>5</v>
       </c>
       <c r="I218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>5</v>
       </c>
       <c r="L218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>5</v>
       </c>
       <c r="O218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ísť</t>
+          <t>nejsť</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -23756,7 +23756,7 @@
         <v>28</v>
       </c>
       <c r="F396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>3</v>
       </c>
       <c r="I396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>3</v>
       </c>
       <c r="L396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>3</v>
       </c>
       <c r="O396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -35476,7 +35476,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>mnoho</t>
+          <t>mnohý</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -35491,7 +35491,7 @@
         <v>44</v>
       </c>
       <c r="F595" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G595" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>8</v>
       </c>
       <c r="L595" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M595" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>8</v>
       </c>
       <c r="O595" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -37069,7 +37069,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>mnoho</t>
+          <t>mnohý</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -37084,7 +37084,7 @@
         <v>46</v>
       </c>
       <c r="F622" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G622" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>1</v>
       </c>
       <c r="I622" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J622" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>1</v>
       </c>
       <c r="L622" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M622" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>1</v>
       </c>
       <c r="O622" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>tá</t>
+          <t>táto</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -40930,7 +40930,7 @@
         <v>4</v>
       </c>
       <c r="I687" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J687" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>4</v>
       </c>
       <c r="L687" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M687" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>4</v>
       </c>
       <c r="O687" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
@@ -41376,7 +41376,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>piať</t>
+          <t>päť</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -41391,7 +41391,7 @@
         <v>53</v>
       </c>
       <c r="F695" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G695" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>5</v>
       </c>
       <c r="I695" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J695" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>5</v>
       </c>
       <c r="L695" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M695" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>5</v>
       </c>
       <c r="O695" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696">
@@ -50344,7 +50344,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>oni</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -50359,7 +50359,7 @@
         <v>69</v>
       </c>
       <c r="F847" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G847" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>3</v>
       </c>
       <c r="I847" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J847" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>3</v>
       </c>
       <c r="L847" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M847" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>3</v>
       </c>
       <c r="O847" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="848">
@@ -56775,7 +56775,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>oni</t>
+          <t>on</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -56790,7 +56790,7 @@
         <v>80</v>
       </c>
       <c r="F956" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G956" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>3</v>
       </c>
       <c r="I956" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J956" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>3</v>
       </c>
       <c r="L956" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M956" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>3</v>
       </c>
       <c r="O956" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="957">
@@ -59017,7 +59017,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>stacionárne</t>
+          <t>stacionárny</t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -59032,7 +59032,7 @@
         <v>83</v>
       </c>
       <c r="F994" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G994" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>6</v>
       </c>
       <c r="I994" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J994" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>6</v>
       </c>
       <c r="L994" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M994" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>6</v>
       </c>
       <c r="O994" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="995">
